--- a/Архитектура бизнеса в высокотехнологичных отраслях/Практики/Практика_2_PEST_5P.xlsx
+++ b/Архитектура бизнеса в высокотехнологичных отраслях/Практики/Практика_2_PEST_5P.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\University\Архитектура бизнеса в высокотехнологичных отраслях\Практики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D32647-A1C0-4EBF-BFAC-5A429C2F04B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9385E876-18D6-4265-A2BB-1612DA8119BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PEST" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="159">
   <si>
     <t>Код</t>
   </si>
@@ -100,30 +100,12 @@
     <t>Государственный курс на внедрение ИИ</t>
   </si>
   <si>
-    <t>Тема ИИ получает институциональную поддержку; коммерческую применимость нужно доказывать в конкретном процессе.</t>
-  </si>
-  <si>
-    <t>Официальный текст стратегии устанавливает цели и показатели развития и внедрения ИИ до 2030 года.</t>
-  </si>
-  <si>
-    <t>https://government.ru/docs/all/124098/?page=3</t>
-  </si>
-  <si>
     <t>P3</t>
   </si>
   <si>
     <t>Стимулирование отечественного ПО</t>
   </si>
   <si>
-    <t>У российских заказчиков повышается интерес к локальным решениям; нужны подтверждённое происхождение и совместимость.</t>
-  </si>
-  <si>
-    <t>Правительство фиксирует ускоренный переход предприятий на отечественное ПО и требования к совместимости решений.</t>
-  </si>
-  <si>
-    <t>https://government.ru/news/55236/</t>
-  </si>
-  <si>
     <t>E1</t>
   </si>
   <si>
@@ -365,6 +347,171 @@
   </si>
   <si>
     <t>Выскоке</t>
+  </si>
+  <si>
+    <t>Расчёт итоговой PEST-оценки</t>
+  </si>
+  <si>
+    <t>Средневзвешенная оценка (1–5)</t>
+  </si>
+  <si>
+    <t>Интерпретация</t>
+  </si>
+  <si>
+    <t>Формула</t>
+  </si>
+  <si>
+    <t>Σ(I × средняя экспертная оценка) / ΣI</t>
+  </si>
+  <si>
+    <t>Вес каждого фактора = I / ΣI; итоговая оценка равна сумме весовых оценок и пересчитывается при изменении I или экспертных баллов.</t>
+  </si>
+  <si>
+    <t>Методика</t>
+  </si>
+  <si>
+    <t>I: 1 — незначительное, 2 — заметное при существенном изменении, 3 — сильное даже при небольшом изменении.</t>
+  </si>
+  <si>
+    <t>Оценка эксперта: от 1 до 5 для вероятности сохранения или усиления воздействия в ближайшие 12–24 месяца.</t>
+  </si>
+  <si>
+    <t>Средняя оценка = среднее трёх оценок; вес = I / сумма I; весовая оценка = вес × средняя оценка.</t>
+  </si>
+  <si>
+    <t>Федеральным органам предписано учитывать Национальную стратегию развития ИИ при подготовке отраслевых стратегий и государственных программ, а федеральный проект «Искусственный интеллект» включить в национальный проект по формированию экономики данных. Это усиливает институциональную поддержку решений на основе ИИ.</t>
+  </si>
+  <si>
+    <t>Указ Президента РФ от 15.02.2024 № 124 об актуализации Национальной стратегии развития искусственного интеллекта до 2030 года</t>
+  </si>
+  <si>
+    <t>С 1 января 2025 года расходы на приобретение прав на программы, базы данных и программно-аппаратные комплексы, включённые в единый реестр российского ПО, могут учитываться с коэффициентом 2. Это создаёт налоговый стимул для выбора отечественных программных решений.</t>
+  </si>
+  <si>
+    <t>Письмо Департамента налоговой политики Минфина России от 05.12.2024 № 03-03-06/122830 о применении коэффициента 2 к расходам на российское ПО</t>
+  </si>
+  <si>
+    <t>https://base.garant.ru/408559959/</t>
+  </si>
+  <si>
+    <t>https://base.garant.ru/411138705/</t>
+  </si>
+  <si>
+    <t>Вероятное изменение</t>
+  </si>
+  <si>
+    <t>Влияение на компанию</t>
+  </si>
+  <si>
+    <t>Варианты решения</t>
+  </si>
+  <si>
+    <t>Контроль обработки персональных данных и ответственность за утечки будут усиливаться. Заказчики станут строже проверять поставщиков аналитических систем.</t>
+  </si>
+  <si>
+    <t>Вырастут расходы Cyberbara на защиту данных, документирование процессов и юридическое сопровождение. Нарушение требований может привести к штрафам и потере доверия клиентов.</t>
+  </si>
+  <si>
+    <t>Применять минимизацию и обезличивание данных, разграничение доступа и журналирование операций. До запуска интеграции проводить аудит состава собираемых данных и условий их хранения.</t>
+  </si>
+  <si>
+    <t>Поддержка ИИ будет расширяться через государственные программы, отраслевые стратегии и проекты цифровой трансформации. Одновременно появятся дополнительные требования к эффективности и безопасности решений.</t>
+  </si>
+  <si>
+    <t>Расширятся возможности участия Cyberbara в корпоративных и государственных проектах. Для заключения контрактов потребуется доказывать практический эффект и соответствие установленным требованиям.</t>
+  </si>
+  <si>
+    <t>Проводить пилоты с заранее установленными показателями эффективности. Связывать предложение Cyberbara с задачами цифровой трансформации заказчика и документировать полученный результат.</t>
+  </si>
+  <si>
+    <t>Налоговые стимулы и требования к применению российского ПО будут поддерживать спрос на отечественные решения. Значение включения продукта и его компонентов в профильные реестры возрастёт.</t>
+  </si>
+  <si>
+    <t>Cyberbara получит преимущество перед иностранными аналогами, но заказчики будут проверять происхождение компонентов и совместимость со своей инфраструктурой. Использование неподтверждённых иностранных зависимостей может ограничить продажи.</t>
+  </si>
+  <si>
+    <t>Составить перечень используемых программных компонентов и постепенно заменять критические иностранные зависимости. Подготовить продукт к включению в реестр российского ПО и проводить тестирование совместимости.</t>
+  </si>
+  <si>
+    <t>Стоимость заёмного финансирования может оставаться высокой, даже если ставка будет постепенно снижаться. Организации продолжат осторожно согласовывать новые ИТ-проекты.</t>
+  </si>
+  <si>
+    <t>Продажный цикл Cyberbara может увеличиться, а заказчики будут сокращать бюджет и масштаб пилотного внедрения. Особое значение получит короткий и понятный срок окупаемости.</t>
+  </si>
+  <si>
+    <t>Предлагать ограниченный платный пилот с поэтапным расширением. В коммерческом предложении показывать ожидаемую экономию, срок окупаемости и стоимость владения.</t>
+  </si>
+  <si>
+    <t>Расходы организаций на цифровизацию продолжат расти, но бюджеты будут распределяться в пользу решений с измеримым результатом. Конкуренция между ИТ-проектами за финансирование усилится.</t>
+  </si>
+  <si>
+    <t>Для Cyberbara расширяется потенциальный рынок, но сам рост расходов не гарантирует спрос на конкретный продукт. Заказчики будут сравнивать систему с другими направлениями цифровизации.</t>
+  </si>
+  <si>
+    <t>Выбирать организации с действующими программами цифровой трансформации. Обосновывать внедрение через снижение трудозатрат, ускорение аналитики и уменьшение репутационных рисков.</t>
+  </si>
+  <si>
+    <t>Вычислительные ресурсы и открытые модели могут дешеветь, но интеграция, подготовка данных и сопровождение останутся значительными статьями расходов. Заказчики будут требовать прозрачного расчёта полной стоимости.</t>
+  </si>
+  <si>
+    <t>Высокая стоимость может ограничить число клиентов и снизить маржинальность индивидуальных внедрений. Особенно сложно будет работать с небольшими организациями.</t>
+  </si>
+  <si>
+    <t>Разработать модульные тарифы и облачную версию с ограничениями по объёму обработки. Повторно использовать готовые интеграции и контролировать затраты на модели и инфраструктуру.</t>
+  </si>
+  <si>
+    <t>Аудитория продолжит переходить между социальными сетями и мессенджерами. Значимость отдельных источников будет меняться быстрее, чем раньше.</t>
+  </si>
+  <si>
+    <t>Анализ только одной площадки будет давать неполное представление об информационном поле. Ценность Cyberbara будет зависеть от количества и качества поддерживаемых источников.</t>
+  </si>
+  <si>
+    <t>Развивать модульную систему подключаемых каналов и регулярно оценивать полноту их данных. В отчётах указывать охват источников и существующие ограничения анализа.</t>
+  </si>
+  <si>
+    <t>Влияние интернет-отзывов сохранится, но одновременно возрастёт количество заказных и автоматически созданных публикаций. Проверка достоверности отзывов станет важнее их простого сбора.</t>
+  </si>
+  <si>
+    <t>Спрос на анализ репутации может вырасти, однако ложные сигналы способны снизить качество выводов Cyberbara. Ошибочная оценка тональности создаст риск неправильных управленческих решений.</t>
+  </si>
+  <si>
+    <t>Ввести оценку надёжности источника и выявление подозрительной активности. Значимые выводы подтверждать примерами публикаций и возможностью ручной проверки.</t>
+  </si>
+  <si>
+    <t>Пользователи и заказчики будут требовать большей прозрачности алгоритмов и контроля над использованием данных. Недоверие к полностью автоматическим решениям сохранится.</t>
+  </si>
+  <si>
+    <t>Непрозрачные выводы могут замедлить внедрение Cyberbara и вызвать репутационные риски. Заказчики будут ожидать возможности проверить основания каждой рекомендации.</t>
+  </si>
+  <si>
+    <t>Добавить ссылки на исходные сообщения, объяснение причин оценки и уровень уверенности модели. Окончательные значимые решения оставлять за человеком и минимизировать сбор персональных данных.</t>
+  </si>
+  <si>
+    <t>Количество и качество открытых русскоязычных моделей будут расти, а стоимость их использования — снижаться. Базовые функции текстового анализа станут доступнее конкурентам.</t>
+  </si>
+  <si>
+    <t>Cyberbara сможет сократить расходы на разработку, но технологическое преимущество от использования одной модели уменьшится. Конкуренция сместится в область данных, интеграций и отраслевой аналитики.</t>
+  </si>
+  <si>
+    <t>Использовать архитектуру, позволяющую заменять модели без переработки всей системы. Регулярно сравнивать модели, а продукт отличать качеством интеграций и специализированных аналитических функций.</t>
+  </si>
+  <si>
+    <t>Организации будут переходить от экспериментального применения текстового ИИ к его включению в постоянные рабочие процессы. Требования к точности, интеграции и стабильности возрастут.</t>
+  </si>
+  <si>
+    <t>Потенциальный спрос на Cyberbara увеличится, но заказчики будут ожидать промышленного качества и подтверждённых результатов. Ошибки модели станут заметнее при регулярном использовании.</t>
+  </si>
+  <si>
+    <t>Сосредоточиться на конкретных сценариях анализа и установить измеримые показатели качества. Использовать ручную проверку критичных выводов и готовые интеграции с системами заказчика.</t>
+  </si>
+  <si>
+    <t>Ограничения платформенных API сохранятся и могут изменяться без участия Cyberbara. Площадки могут ужесточать правила доступа к сообщениям и пользовательским данным.</t>
+  </si>
+  <si>
+    <t>Система может получать неполные данные, а отдельные интеграции — временно переставать работать. Это снижает достоверность мониторинга и создаёт зависимость от сторонней платформы.</t>
+  </si>
+  <si>
+    <t>Контролировать полноту поступающих данных и уведомлять заказчика об обнаруженных пробелах. Использовать разрешённые права бота, модульные коннекторы и дополнительные источники информации.</t>
   </si>
 </sst>
 </file>
@@ -375,12 +522,20 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -426,8 +581,65 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF595959"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF263238"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF5E6973"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF263D5B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF263238"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,8 +651,13 @@
         <fgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -460,21 +677,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,64 +746,108 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -654,6 +900,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2020455</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>92942</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1" descr="Предварительный просмотр изображения">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD5AA03F-8A75-4774-BB05-6F8CFA98A33A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9582728" y="4687455"/>
+          <a:ext cx="15921759" cy="8993909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -919,23 +1231,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="245.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.453125" customWidth="1"/>
     <col min="5" max="5" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="165.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="144.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="204.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="234.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="205.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="165.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="144.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.5">
+    <row r="1" spans="1:16" ht="17.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -969,14 +1284,23 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N1" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:16" ht="18">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -986,7 +1310,7 @@
       <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="30" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="4">
@@ -1013,14 +1337,23 @@
         <f t="shared" ref="K2:K13" si="2">IF(I2="","",J2*I2)</f>
         <v>0.5</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="O2" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="P2" s="32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:16" ht="31">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1030,8 +1363,8 @@
       <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
+      <c r="D3" s="30" t="s">
+        <v>114</v>
       </c>
       <c r="E3" s="4">
         <v>2</v>
@@ -1057,25 +1390,34 @@
         <f t="shared" si="2"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="L3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18">
+      <c r="L3" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M3" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="O3" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="31">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="E4" s="4">
         <v>2</v>
@@ -1101,25 +1443,34 @@
         <f t="shared" si="2"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="L4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18">
+      <c r="L4" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="N4" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="O4" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="P4" s="34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="18">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="4">
         <v>3</v>
@@ -1145,25 +1496,34 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="L5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18">
+      <c r="L5" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="N5" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="18">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>37</v>
+      <c r="D6" s="30" t="s">
+        <v>31</v>
       </c>
       <c r="E6" s="4">
         <v>3</v>
@@ -1189,25 +1549,34 @@
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="L6" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18">
+      <c r="L6" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="M6" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="O6" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="28">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
@@ -1233,25 +1602,34 @@
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18">
+      <c r="L7" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="O7" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="28">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="E8" s="4">
         <v>3</v>
@@ -1277,25 +1655,34 @@
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18">
+      <c r="L8" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="O8" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="P8" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="18">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>53</v>
+      <c r="D9" s="30" t="s">
+        <v>47</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -1321,25 +1708,34 @@
         <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18">
+      <c r="L9" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="O9" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="18">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>52</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1365,25 +1761,34 @@
         <f t="shared" si="2"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="18">
+      <c r="L10" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="M10" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="N10" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="O10" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="18">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>58</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -1409,25 +1814,34 @@
         <f t="shared" si="2"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18">
+      <c r="L11" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="M11" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="N11" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="O11" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="18">
       <c r="A12" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>69</v>
+      <c r="D12" s="30" t="s">
+        <v>63</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -1453,25 +1867,34 @@
         <f t="shared" si="2"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="L12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="18">
+      <c r="L12" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="M12" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="N12" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="O12" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" s="32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="18">
       <c r="A13" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="E13" s="4">
         <v>3</v>
@@ -1497,16 +1920,25 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="L13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18">
+      <c r="L13" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="M13" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="N13" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="P13" s="32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="18">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1523,14 +1955,114 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <f>IF(COUNT(I2:I13)=12,SUM(K2:K13),"")</f>
         <v>4.3666666666666663</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="34"/>
+    </row>
+    <row r="16" spans="1:16" ht="18">
+      <c r="A16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:4" ht="14.5" customHeight="1">
+      <c r="A17" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18">
+      <c r="A18" s="19">
+        <f>K14</f>
+        <v>4.3666666666666663</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="15" t="str">
+        <f>IF(A18="","",IF(A18&gt;=4,"Высокое влияние",IF(A18&gt;=3,"Значимое влияние","Умеренное влияние")))</f>
+        <v>Высокое влияние</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18">
+      <c r="A19" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+    </row>
+    <row r="22" spans="1:4" s="22" customFormat="1" ht="18">
+      <c r="A22" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18">
+      <c r="A23" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+    </row>
+    <row r="24" spans="1:4" ht="18">
+      <c r="A24" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+    </row>
+    <row r="25" spans="1:4" ht="18">
+      <c r="A25" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+    </row>
+    <row r="26" spans="1:4" ht="18">
+      <c r="A26" s="13"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A22:XFD22"/>
+    <mergeCell ref="A23:D23"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" sqref="F2:H13" xr:uid="{25D8BFDE-7D78-4EA4-93C7-7A2D41E74BF8}">
       <formula1>1</formula1>
@@ -1542,21 +2074,21 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{D4730FA7-25F4-4836-97A9-DFB4AE88E2BE}"/>
-    <hyperlink ref="M3" r:id="rId2" xr:uid="{44ACAEE9-A94C-4772-B1C5-B9E54940FC33}"/>
-    <hyperlink ref="M4" r:id="rId3" xr:uid="{3B65A4A5-8F39-44ED-A9A1-1BD6CA2F0775}"/>
-    <hyperlink ref="M5" r:id="rId4" xr:uid="{CE347C20-9EBE-49ED-94EF-5D77D7528897}"/>
-    <hyperlink ref="M6" r:id="rId5" xr:uid="{1DF6D165-5B5C-4817-906F-D889BA450DCD}"/>
-    <hyperlink ref="M7" r:id="rId6" xr:uid="{AC5946E3-BD60-44D9-93D9-F3D83F51E83F}"/>
-    <hyperlink ref="M8" r:id="rId7" xr:uid="{4C6645E1-9926-49D9-8DE3-6E1F92E8A5C2}"/>
-    <hyperlink ref="M9" r:id="rId8" xr:uid="{4056757E-9F40-4571-9505-CDDD723978D3}"/>
-    <hyperlink ref="M10" r:id="rId9" xr:uid="{752C88AE-B694-45BF-B31A-C76553833F85}"/>
-    <hyperlink ref="M11" r:id="rId10" xr:uid="{F670A93C-085B-4648-B85C-5F7146D6FC48}"/>
-    <hyperlink ref="M12" r:id="rId11" xr:uid="{61DE23D0-067E-4BFC-A14C-5823096F8682}"/>
-    <hyperlink ref="M13" r:id="rId12" xr:uid="{C48047BC-EB52-46BA-B7A5-9A5B558CE306}"/>
+    <hyperlink ref="P2" r:id="rId1" xr:uid="{D4730FA7-25F4-4836-97A9-DFB4AE88E2BE}"/>
+    <hyperlink ref="P5" r:id="rId2" xr:uid="{CE347C20-9EBE-49ED-94EF-5D77D7528897}"/>
+    <hyperlink ref="P6" r:id="rId3" xr:uid="{1DF6D165-5B5C-4817-906F-D889BA450DCD}"/>
+    <hyperlink ref="P7" r:id="rId4" xr:uid="{AC5946E3-BD60-44D9-93D9-F3D83F51E83F}"/>
+    <hyperlink ref="P8" r:id="rId5" xr:uid="{4C6645E1-9926-49D9-8DE3-6E1F92E8A5C2}"/>
+    <hyperlink ref="P9" r:id="rId6" xr:uid="{4056757E-9F40-4571-9505-CDDD723978D3}"/>
+    <hyperlink ref="P10" r:id="rId7" xr:uid="{752C88AE-B694-45BF-B31A-C76553833F85}"/>
+    <hyperlink ref="P11" r:id="rId8" xr:uid="{F670A93C-085B-4648-B85C-5F7146D6FC48}"/>
+    <hyperlink ref="P12" r:id="rId9" xr:uid="{61DE23D0-067E-4BFC-A14C-5823096F8682}"/>
+    <hyperlink ref="P13" r:id="rId10" xr:uid="{C48047BC-EB52-46BA-B7A5-9A5B558CE306}"/>
+    <hyperlink ref="P3" r:id="rId11" xr:uid="{AC927774-C974-42B1-8350-7DFFA750A1E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <drawing r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -1577,41 +2109,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" ht="36">
+      <c r="A2" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" ht="36">
-      <c r="A2" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="C2" s="3">
         <v>9</v>
@@ -1631,18 +2163,18 @@
         <v>Высокое</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>90</v>
+        <v>83</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36">
-      <c r="A3" s="11" t="s">
-        <v>91</v>
+      <c r="A3" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3">
         <v>8</v>
@@ -1662,18 +2194,18 @@
         <v>Высокое</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="36">
-      <c r="A4" s="11" t="s">
-        <v>95</v>
+      <c r="A4" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3">
         <v>9</v>
@@ -1693,18 +2225,18 @@
         <v>Высокое</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="36">
-      <c r="A5" s="11" t="s">
-        <v>99</v>
+      <c r="A5" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C5" s="3">
         <v>8</v>
@@ -1724,18 +2256,18 @@
         <v>Высокое</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="36">
-      <c r="A6" s="11" t="s">
-        <v>103</v>
+      <c r="A6" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C6" s="3">
         <v>8</v>
@@ -1755,37 +2287,37 @@
         <v>Высокое</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>106</v>
+        <v>99</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.5">
-      <c r="A7" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="11">
+      <c r="A7" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="9">
         <v>10.6</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>109</v>
+      <c r="G7" s="26" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="35" customHeight="1">
-      <c r="A8" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="18"/>
+      <c r="A8" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="3">
